--- a/media/exports/reports/2026-06/cost-to-raise.xlsx
+++ b/media/exports/reports/2026-06/cost-to-raise.xlsx
@@ -24,48 +24,58 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;¢&quot;;[Red](0&quot;¢&quot;)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
@@ -98,39 +108,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -954,8 +964,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 cost-to-raise.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1624,8 +1634,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 cost-to-raise.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2447,8 +2457,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 cost-to-raise.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-06/cost-to-raise.xlsx
+++ b/media/exports/reports/2026-06/cost-to-raise.xlsx
@@ -12,7 +12,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="June_all_fundraising">'Report'!$B$9</definedName>
+    <definedName name="Year_to_date_Jul_to_Jun_2026">'Report'!$B$10</definedName>
+    <definedName name="June_Grants">'Report'!$B$34</definedName>
+    <definedName name="Year_to_date_Jul_to_Jun_2026_2">'Report'!$B$35</definedName>
+    <definedName name="June_Donations">'Report'!$B$45</definedName>
+    <definedName name="Year_to_date_Jul_to_Jun_2026_3">'Report'!$B$46</definedName>
+    <definedName name="June_Fundraising_events">'Report'!$B$56</definedName>
+    <definedName name="Year_to_date_Jul_to_Jun_2026_4">'Report'!$B$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$I$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -125,7 +136,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -218,6 +231,288 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Cost to raise a dollar, by source, June 2026 (cents)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Cost to raise a dollar</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0&quot;¢&quot;"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$14:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$14:$B$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0&quot;¢&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Grant writing by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Grant writing</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$6:$A$26</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$C$6:$C$26</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="cost_to_raise_Data" displayName="cost_to_raise_Data" ref="A5:I26" headerRowCount="1">
+  <autoFilter ref="A5:I26"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Month"/>
+    <tableColumn id="2" name="Status"/>
+    <tableColumn id="3" name="Grant writing"/>
+    <tableColumn id="4" name="Donor campaigns"/>
+    <tableColumn id="5" name="Event costs"/>
+    <tableColumn id="6" name="Grant income"/>
+    <tableColumn id="7" name="Donations"/>
+    <tableColumn id="8" name="Events"/>
+    <tableColumn id="9" name="Cents per $1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -509,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -528,14 +823,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -616,7 +911,7 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Cost to raise a dollar</t>
         </is>
       </c>
     </row>
@@ -641,340 +936,350 @@
       </c>
     </row>
     <row r="16"/>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>June cost 11¢ to raise each dollar, against 10¢ in May. This financial year to date it has cost 13¢ a dollar.</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>The year-to-date figure is steadier than single months: events make some months jump. Pick a source above to see which one moves it.</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Source: Grants</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>June · Grants</t>
         </is>
       </c>
-      <c r="B25" s="7">
+      <c r="B34" s="7">
         <f>Workings!B39</f>
         <v/>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>May 10¢</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Year to date (Jul to Jun 2026)</t>
         </is>
       </c>
-      <c r="B26" s="7">
+      <c r="B35" s="7">
         <f>Workings!B47</f>
         <v/>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>same period last year: not in the data</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Grants cost 11¢ to raise each dollar this financial year to date ($85,200 of grant writing and reporting for $770,082).</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Usually the cheapest money to raise, as long as the time that goes into applications and acquittals is protected.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Source: Donations</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>June · Donations</t>
         </is>
       </c>
-      <c r="B36" s="7">
+      <c r="B45" s="7">
         <f>Workings!B56</f>
         <v/>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>May 13¢</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Year to date (Jul to Jun 2026)</t>
         </is>
       </c>
-      <c r="B37" s="7">
+      <c r="B46" s="7">
         <f>Workings!B64</f>
         <v/>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>same period last year: not in the data</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Donations cost 15¢ to raise each dollar this financial year to date ($32,800 of donor campaigns for $225,900).</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Steady and cheap, and untied: the money that builds reserves.</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Source: Fundraising events</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>June · Fundraising events</t>
         </is>
       </c>
-      <c r="B47" s="11">
+      <c r="B56" s="11">
         <f>Workings!B72</f>
         <v/>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>May none raised</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Year to date (Jul to Jun 2026)</t>
         </is>
       </c>
-      <c r="B48" s="7">
+      <c r="B57" s="7">
         <f>Workings!B81</f>
         <v/>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>same period last year: not in the data</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Fundraising events cost 41¢ to raise each dollar this financial year to date ($17,800 of event costs for $43,000).</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Usually the dearest money to raise: events are worth counting for what else they bring too (new donors, profile).</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Every source at once</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, by month (cents): every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59"/>
+    <row r="67"/>
+    <row r="68"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A63:D63"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="27" min="0" max="16383" man="1"/>
-    <brk id="49" min="0" max="16383" man="1"/>
+    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="47" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1003,14 +1308,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1940,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1679,14 +1984,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -2458,11 +2763,15 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-06/cost-to-raise.xlsx
+++ b/media/exports/reports/2026-06/cost-to-raise.xlsx
@@ -12,15 +12,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="June_all_fundraising">'Report'!$B$9</definedName>
-    <definedName name="Year_to_date_Jul_to_Jun_2026">'Report'!$B$10</definedName>
-    <definedName name="June_Grants">'Report'!$B$34</definedName>
-    <definedName name="Year_to_date_Jul_to_Jun_2026_2">'Report'!$B$35</definedName>
-    <definedName name="June_Donations">'Report'!$B$45</definedName>
-    <definedName name="Year_to_date_Jul_to_Jun_2026_3">'Report'!$B$46</definedName>
-    <definedName name="June_Fundraising_events">'Report'!$B$56</definedName>
-    <definedName name="Year_to_date_Jul_to_Jun_2026_4">'Report'!$B$57</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$66</definedName>
+    <definedName name="June_all_fundraising">'Report'!$B$10</definedName>
+    <definedName name="Year_to_date_Jul_to_Jun_2026">'Report'!$B$11</definedName>
+    <definedName name="June_Grants">'Report'!$B$35</definedName>
+    <definedName name="Year_to_date_Jul_to_Jun_2026_2">'Report'!$B$36</definedName>
+    <definedName name="June_Donations">'Report'!$B$46</definedName>
+    <definedName name="Year_to_date_Jul_to_Jun_2026_3">'Report'!$B$47</definedName>
+    <definedName name="June_Fundraising_events">'Report'!$B$57</definedName>
+    <definedName name="Year_to_date_Jul_to_Jun_2026_4">'Report'!$B$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$I$26</definedName>
@@ -59,6 +59,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
@@ -79,11 +84,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -125,35 +125,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -297,12 +299,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$14:$A$15</f>
+              <f>'Report'!$A$15:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$14:$B$15</f>
+              <f>'Report'!$B$15:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -449,7 +451,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="1980000"/>
@@ -804,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -830,7 +832,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -838,104 +840,110 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Each dollar raised cost 11¢ in June, and 13¢ a dollar this financial year to date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>What fundraising costs (grant writing, donor campaigns, events) for every dollar it brings in. Pick a source and every number, chart and note follows it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Source: All fundraising</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Source: All fundraising</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>June · all fundraising</t>
-        </is>
-      </c>
-      <c r="B9" s="7">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>May 10¢</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>June · all fundraising</t>
+        </is>
+      </c>
+      <c r="B10" s="8">
+        <f>Workings!B10</f>
+        <v/>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>May 10¢</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Year to date (Jul to Jun 2026)</t>
         </is>
       </c>
-      <c r="B10" s="7">
+      <c r="B11" s="8">
         <f>Workings!B18</f>
         <v/>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>same period last year: not in the data</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, by source, June 2026 (cents)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Cost to raise a dollar</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B16" s="8" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="16"/>
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
@@ -945,339 +953,342 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>June cost 11¢ to raise each dollar, against 10¢ in May. This financial year to date it has cost 13¢ a dollar.</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>The year-to-date figure is steadier than single months: events make some months jump. Pick a source above to see which one moves it.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Source: Grants</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>Source: Grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>June · Grants</t>
-        </is>
-      </c>
-      <c r="B34" s="7">
-        <f>Workings!B39</f>
-        <v/>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>May 10¢</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>June · Grants</t>
+        </is>
+      </c>
+      <c r="B35" s="8">
+        <f>Workings!B39</f>
+        <v/>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>May 10¢</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Year to date (Jul to Jun 2026)</t>
         </is>
       </c>
-      <c r="B35" s="7">
+      <c r="B36" s="8">
         <f>Workings!B47</f>
         <v/>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>same period last year: not in the data</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Grants cost 11¢ to raise each dollar this financial year to date ($85,200 of grant writing and reporting for $770,082).</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Usually the cheapest money to raise, as long as the time that goes into applications and acquittals is protected.</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Source: Donations</t>
-        </is>
-      </c>
-    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>Source: Donations</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>June · Donations</t>
-        </is>
-      </c>
-      <c r="B45" s="7">
-        <f>Workings!B56</f>
-        <v/>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>May 13¢</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>June · Donations</t>
+        </is>
+      </c>
+      <c r="B46" s="8">
+        <f>Workings!B56</f>
+        <v/>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>May 13¢</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Year to date (Jul to Jun 2026)</t>
         </is>
       </c>
-      <c r="B46" s="7">
+      <c r="B47" s="8">
         <f>Workings!B64</f>
         <v/>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>same period last year: not in the data</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Donations cost 15¢ to raise each dollar this financial year to date ($32,800 of donor campaigns for $225,900).</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Steady and cheap, and untied: the money that builds reserves.</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Source: Fundraising events</t>
-        </is>
-      </c>
-    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>Source: Fundraising events</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>June · Fundraising events</t>
-        </is>
-      </c>
-      <c r="B56" s="11">
-        <f>Workings!B72</f>
-        <v/>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>May none raised</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>June · Fundraising events</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>May none raised</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Year to date (Jul to Jun 2026)</t>
         </is>
       </c>
-      <c r="B57" s="7">
+      <c r="B58" s="8">
         <f>Workings!B81</f>
         <v/>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>same period last year: not in the data</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Fundraising events cost 41¢ to raise each dollar this financial year to date ($17,800 of event costs for $43,000).</t>
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Usually the dearest money to raise: events are worth counting for what else they bring too (new donors, profile).</t>
         </is>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Every source at once</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, by month (cents): every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="67"/>
     <row r="68"/>
+    <row r="69"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="25" min="0" max="16383" man="1"/>
-    <brk id="47" min="0" max="16383" man="1"/>
+    <brk id="26" min="0" max="16383" man="1"/>
+    <brk id="48" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1315,13 +1326,13 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, all fundraising, June and May</t>
         </is>
@@ -1335,13 +1346,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
@@ -1391,7 +1402,7 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, all fundraising, year to date</t>
         </is>
@@ -1405,8 +1416,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Year to date</t>
         </is>
@@ -1453,7 +1464,7 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, by source, June 2026</t>
         </is>
@@ -1467,8 +1478,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
@@ -1546,7 +1557,7 @@
     <row r="32"/>
     <row r="33"/>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, grants, June and May</t>
         </is>
@@ -1560,13 +1571,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
@@ -1616,7 +1627,7 @@
     <row r="40"/>
     <row r="41"/>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, grants, year to date</t>
         </is>
@@ -1630,8 +1641,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr"/>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr"/>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Year to date</t>
         </is>
@@ -1678,7 +1689,7 @@
     <row r="49"/>
     <row r="50"/>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, donations, June and May</t>
         </is>
@@ -1692,13 +1703,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr"/>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr"/>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
@@ -1748,7 +1759,7 @@
     <row r="57"/>
     <row r="58"/>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, donations, year to date</t>
         </is>
@@ -1762,8 +1773,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr"/>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr"/>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Year to date</t>
         </is>
@@ -1810,7 +1821,7 @@
     <row r="66"/>
     <row r="67"/>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, fundraising events, June and May</t>
         </is>
@@ -1824,13 +1835,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr"/>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr"/>
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
@@ -1872,7 +1883,7 @@
     <row r="74"/>
     <row r="75"/>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, fundraising events, year to date</t>
         </is>
@@ -1886,8 +1897,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr"/>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr"/>
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Year to date</t>
         </is>
@@ -1940,7 +1951,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1991,53 +2002,53 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: June 2026 · Data status: May 2026 locked · Jun 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Grant writing</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Donor campaigns</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Event costs</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Grant income</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Cents per $1</t>
         </is>
@@ -2763,7 +2774,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-raise.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
